--- a/data/trans_orig/P79A5_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P79A5_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si tiene resuelto el retraso en los pagos de los impuestos relacionados con vehículos en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si tiene resuelto el retraso en los pagos de los impuestos relacionados con vehículos, IBI, etc en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -770,12 +770,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>75,19%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -873,7 +873,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1546</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5948</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3975</t>
+          <t>4557</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1078,12 +1078,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7956</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,04%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>51,79%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3370</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8637</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>66,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4833</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>34,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>81,84%</t>
         </is>
       </c>
     </row>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2208</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3210</t>
+          <t>3310</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8698</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>65,15%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>15189</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,27 +1754,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7990</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>4703</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3203</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7607</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>13520</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16248</t>
+          <t>17710</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>74,78%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>87,71%</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4265</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1892,7 +1892,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3558</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1984</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5884</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>49,4%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>9653</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18080</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>11253</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>7601</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>13992</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>77,12%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,27 +2132,27 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5214</t>
+          <t>6099</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16050</t>
+          <t>17353</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>12555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18705</t>
+          <t>20302</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>92,79%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>868</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6903</t>
+          <t>7504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>618</t>
+          <t>673</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1178</t>
+          <t>1576</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8191</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14051</t>
+          <t>15105</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5832</t>
+          <t>6772</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19883</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,27 +2440,27 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2810</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>862</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2475,27 +2475,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6436</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5621</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>75,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10327</t>
+          <t>11228</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,25%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1073</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>386</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>1798</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1437</t>
+          <t>1513</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>382</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3883</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10683</t>
+          <t>11610</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7425</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>34241</t>
+          <t>36725</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27691</t>
+          <t>29680</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38472</t>
+          <t>41681</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>30550</t>
+          <t>34566</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>28921</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34664</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>64791</t>
+          <t>71291</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>56683</t>
+          <t>61709</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>70548</t>
+          <t>77258</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>8791</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>5227</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15341</t>
+          <t>17228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5181</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>15584</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>20122</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>14155</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26194</t>
+          <t>29704</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,49%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>43032</t>
+          <t>46908</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>39845</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>82877</t>
+          <t>91413</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
